--- a/00_Data/Optimisation_tests/Heat_and_smoke_test_results.xlsx
+++ b/00_Data/Optimisation_tests/Heat_and_smoke_test_results.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uq-my.sharepoint.com/personal/uqfchar1_uq_edu_au/Documents/Desktop/GitHub/Allocasuarina_germfire/00_Data/Optimisation_tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BBB094D-C082-F24A-96BB-9B1C19F0E29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6BBB094D-C082-F24A-96BB-9B1C19F0E29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C11965-00AF-49DC-88F9-1A4C2A21DD6C}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="500" windowWidth="27640" windowHeight="15860" activeTab="1" xr2:uid="{F1DC6946-48FA-4C44-B20B-CA56E613B76C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F1DC6946-48FA-4C44-B20B-CA56E613B76C}"/>
   </bookViews>
   <sheets>
     <sheet name="Heat_shocks_test" sheetId="1" r:id="rId1"/>
     <sheet name="Smoke_tests" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -541,9 +541,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF57A7B-98C2-8B41-AE8C-064351610DDA}">
   <dimension ref="A1:Z157"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="25" max="25" width="20.4140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -705,7 +708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -784,7 +787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -863,7 +866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -945,7 +948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>21</v>
       </c>
@@ -1252,7 +1255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D10" t="s">
         <v>22</v>
       </c>
@@ -1322,7 +1325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
         <v>23</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>24</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1541,7 +1544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
         <v>21</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>22</v>
       </c>
@@ -1681,7 +1684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
         <v>23</v>
       </c>
@@ -1754,7 +1757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
         <v>24</v>
       </c>
@@ -1824,7 +1827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1903,7 +1906,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>21</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
         <v>22</v>
       </c>
@@ -2043,7 +2046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
         <v>23</v>
       </c>
@@ -2113,7 +2116,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
         <v>24</v>
       </c>
@@ -2186,7 +2189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -2268,7 +2271,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D24" t="s">
         <v>21</v>
       </c>
@@ -2341,7 +2344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
         <v>22</v>
       </c>
@@ -2411,7 +2414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D26" t="s">
         <v>23</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D27" t="s">
         <v>24</v>
       </c>
@@ -2551,7 +2554,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2630,7 +2633,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
         <v>21</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D30" t="s">
         <v>22</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D31" t="s">
         <v>23</v>
       </c>
@@ -2840,7 +2843,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D32" t="s">
         <v>24</v>
       </c>
@@ -2910,7 +2913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2989,7 +2992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D34" t="s">
         <v>21</v>
       </c>
@@ -3059,7 +3062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D35" t="s">
         <v>22</v>
       </c>
@@ -3129,7 +3132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D36" t="s">
         <v>23</v>
       </c>
@@ -3199,7 +3202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
         <v>24</v>
       </c>
@@ -3269,7 +3272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3348,7 +3351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D39" t="s">
         <v>21</v>
       </c>
@@ -3418,7 +3421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D40" t="s">
         <v>22</v>
       </c>
@@ -3488,7 +3491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D41" t="s">
         <v>23</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D42" t="s">
         <v>24</v>
       </c>
@@ -3628,7 +3631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3710,7 +3713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D44" t="s">
         <v>21</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D45" t="s">
         <v>22</v>
       </c>
@@ -3850,7 +3853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D46" t="s">
         <v>23</v>
       </c>
@@ -3920,7 +3923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D47" t="s">
         <v>24</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -4069,7 +4072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D49" t="s">
         <v>21</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D50" t="s">
         <v>22</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D51" t="s">
         <v>23</v>
       </c>
@@ -4282,7 +4285,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D52" t="s">
         <v>24</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -4431,7 +4434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D54" t="s">
         <v>21</v>
       </c>
@@ -4501,7 +4504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D55" t="s">
         <v>22</v>
       </c>
@@ -4571,7 +4574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D56" t="s">
         <v>23</v>
       </c>
@@ -4641,7 +4644,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D57" t="s">
         <v>24</v>
       </c>
@@ -4711,7 +4714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -4790,7 +4793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D59" t="s">
         <v>21</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D60" t="s">
         <v>22</v>
       </c>
@@ -4930,7 +4933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D61" t="s">
         <v>23</v>
       </c>
@@ -5000,7 +5003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D62" t="s">
         <v>24</v>
       </c>
@@ -5070,7 +5073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -5149,7 +5152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D64" t="s">
         <v>21</v>
       </c>
@@ -5219,7 +5222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D65" t="s">
         <v>22</v>
       </c>
@@ -5289,7 +5292,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D66" t="s">
         <v>23</v>
       </c>
@@ -5359,7 +5362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D67" t="s">
         <v>24</v>
       </c>
@@ -5429,7 +5432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -5508,7 +5511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D69" t="s">
         <v>21</v>
       </c>
@@ -5578,7 +5581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D70" t="s">
         <v>22</v>
       </c>
@@ -5648,7 +5651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D71" t="s">
         <v>23</v>
       </c>
@@ -5721,7 +5724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D72" t="s">
         <v>24</v>
       </c>
@@ -5791,7 +5794,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -5870,7 +5873,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D74" t="s">
         <v>21</v>
       </c>
@@ -5940,7 +5943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D75" t="s">
         <v>22</v>
       </c>
@@ -6010,7 +6013,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D76" t="s">
         <v>23</v>
       </c>
@@ -6080,7 +6083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D77" t="s">
         <v>24</v>
       </c>
@@ -6150,7 +6153,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -6229,7 +6232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D79" t="s">
         <v>21</v>
       </c>
@@ -6299,7 +6302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D80" t="s">
         <v>22</v>
       </c>
@@ -6372,7 +6375,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D81" t="s">
         <v>23</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D82" t="s">
         <v>24</v>
       </c>
@@ -6512,7 +6515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -6591,7 +6594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D84" t="s">
         <v>21</v>
       </c>
@@ -6661,7 +6664,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D85" t="s">
         <v>22</v>
       </c>
@@ -6731,7 +6734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D86" t="s">
         <v>23</v>
       </c>
@@ -6801,7 +6804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D87" t="s">
         <v>24</v>
       </c>
@@ -6871,7 +6874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D89" t="s">
         <v>21</v>
       </c>
@@ -7020,7 +7023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D90" t="s">
         <v>22</v>
       </c>
@@ -7090,7 +7093,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D91" t="s">
         <v>23</v>
       </c>
@@ -7160,7 +7163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D92" t="s">
         <v>24</v>
       </c>
@@ -7230,7 +7233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -7309,7 +7312,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D94" t="s">
         <v>21</v>
       </c>
@@ -7379,7 +7382,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D95" t="s">
         <v>22</v>
       </c>
@@ -7449,7 +7452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D96" t="s">
         <v>23</v>
       </c>
@@ -7519,7 +7522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D97" t="s">
         <v>24</v>
       </c>
@@ -7589,7 +7592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -7668,7 +7671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D99" t="s">
         <v>21</v>
       </c>
@@ -7738,7 +7741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D100" t="s">
         <v>22</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D101" t="s">
         <v>23</v>
       </c>
@@ -7878,7 +7881,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D102" t="s">
         <v>24</v>
       </c>
@@ -7948,7 +7951,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -8027,7 +8030,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D104" t="s">
         <v>21</v>
       </c>
@@ -8097,7 +8100,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D105" t="s">
         <v>22</v>
       </c>
@@ -8167,7 +8170,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D106" t="s">
         <v>23</v>
       </c>
@@ -8237,7 +8240,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D107" t="s">
         <v>24</v>
       </c>
@@ -8307,7 +8310,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>16</v>
       </c>
@@ -8386,7 +8389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D109" t="s">
         <v>21</v>
       </c>
@@ -8456,7 +8459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D110" t="s">
         <v>22</v>
       </c>
@@ -8526,7 +8529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D111" t="s">
         <v>23</v>
       </c>
@@ -8596,7 +8599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.4">
       <c r="D112" t="s">
         <v>24</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>16</v>
       </c>
@@ -8745,7 +8748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D114" t="s">
         <v>21</v>
       </c>
@@ -8815,7 +8818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D115" t="s">
         <v>22</v>
       </c>
@@ -8885,7 +8888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D116" t="s">
         <v>23</v>
       </c>
@@ -8955,7 +8958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D117" t="s">
         <v>24</v>
       </c>
@@ -9025,7 +9028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>16</v>
       </c>
@@ -9104,7 +9107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D119" t="s">
         <v>21</v>
       </c>
@@ -9174,7 +9177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D120" t="s">
         <v>22</v>
       </c>
@@ -9244,7 +9247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D121" t="s">
         <v>23</v>
       </c>
@@ -9314,7 +9317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D122" t="s">
         <v>24</v>
       </c>
@@ -9384,7 +9387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -9463,7 +9466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D124" t="s">
         <v>21</v>
       </c>
@@ -9533,7 +9536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D125" t="s">
         <v>22</v>
       </c>
@@ -9603,7 +9606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D126" t="s">
         <v>23</v>
       </c>
@@ -9673,7 +9676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D127" t="s">
         <v>24</v>
       </c>
@@ -9746,7 +9749,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -9825,7 +9828,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D129" t="s">
         <v>21</v>
       </c>
@@ -9895,7 +9898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D130" t="s">
         <v>22</v>
       </c>
@@ -9965,7 +9968,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D131" t="s">
         <v>23</v>
       </c>
@@ -10038,7 +10041,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D132" t="s">
         <v>24</v>
       </c>
@@ -10111,7 +10114,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -10190,7 +10193,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D134" t="s">
         <v>21</v>
       </c>
@@ -10260,7 +10263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D135" t="s">
         <v>22</v>
       </c>
@@ -10330,7 +10333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D136" t="s">
         <v>23</v>
       </c>
@@ -10400,7 +10403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D137" t="s">
         <v>24</v>
       </c>
@@ -10470,7 +10473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -10549,7 +10552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D139" t="s">
         <v>21</v>
       </c>
@@ -10619,7 +10622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D140" t="s">
         <v>22</v>
       </c>
@@ -10689,7 +10692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D141" t="s">
         <v>23</v>
       </c>
@@ -10759,7 +10762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D142" t="s">
         <v>24</v>
       </c>
@@ -10829,7 +10832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -10908,7 +10911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D144" t="s">
         <v>21</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D145" t="s">
         <v>22</v>
       </c>
@@ -11048,7 +11051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D146" t="s">
         <v>23</v>
       </c>
@@ -11121,7 +11124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D147" t="s">
         <v>24</v>
       </c>
@@ -11191,7 +11194,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -11270,7 +11273,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D149" t="s">
         <v>21</v>
       </c>
@@ -11340,7 +11343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D150" t="s">
         <v>22</v>
       </c>
@@ -11410,7 +11413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D151" t="s">
         <v>23</v>
       </c>
@@ -11480,7 +11483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D152" t="s">
         <v>24</v>
       </c>
@@ -11550,7 +11553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -11629,7 +11632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D154" t="s">
         <v>21</v>
       </c>
@@ -11699,7 +11702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D155" t="s">
         <v>22</v>
       </c>
@@ -11772,7 +11775,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D156" t="s">
         <v>23</v>
       </c>
@@ -11842,7 +11845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="157" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:26" x14ac:dyDescent="0.4">
       <c r="D157" t="s">
         <v>24</v>
       </c>
@@ -11920,7 +11923,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D3239D-E2B3-3E46-BDE4-BB2E3D09F4AC}">
   <dimension ref="A1:W55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="4" width="9.1640625" customWidth="1"/>
     <col min="5" max="18" width="8.6640625" customWidth="1"/>
@@ -11930,7 +11933,7 @@
     <col min="22" max="22" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12001,7 +12004,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -12071,7 +12074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>14</v>
       </c>
@@ -12138,7 +12141,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>15</v>
       </c>
@@ -12202,7 +12205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -12272,7 +12275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -12339,7 +12342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -12406,7 +12409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12476,7 +12479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>24</v>
       </c>
@@ -12540,7 +12543,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D10" t="s">
         <v>38</v>
       </c>
@@ -12601,7 +12604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
         <v>39</v>
       </c>
@@ -12662,7 +12665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -12729,7 +12732,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
         <v>24</v>
       </c>
@@ -12790,7 +12793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
         <v>38</v>
       </c>
@@ -12848,7 +12851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>39</v>
       </c>
@@ -12909,7 +12912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
         <v>15</v>
       </c>
@@ -12976,7 +12979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
         <v>24</v>
       </c>
@@ -13037,7 +13040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
         <v>38</v>
       </c>
@@ -13098,7 +13101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>39</v>
       </c>
@@ -13159,7 +13162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -13229,7 +13232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
         <v>24</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
         <v>38</v>
       </c>
@@ -13351,7 +13354,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D23" t="s">
         <v>39</v>
       </c>
@@ -13412,7 +13415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
         <v>18</v>
       </c>
@@ -13479,7 +13482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D25" t="s">
         <v>24</v>
       </c>
@@ -13540,7 +13543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D26" t="s">
         <v>38</v>
       </c>
@@ -13601,7 +13604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D27" t="s">
         <v>39</v>
       </c>
@@ -13662,7 +13665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
         <v>19</v>
       </c>
@@ -13729,7 +13732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D29" t="s">
         <v>24</v>
       </c>
@@ -13790,7 +13793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D30" t="s">
         <v>38</v>
       </c>
@@ -13851,7 +13854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D31" t="s">
         <v>39</v>
       </c>
@@ -13912,7 +13915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -13982,7 +13985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D33" t="s">
         <v>24</v>
       </c>
@@ -14043,7 +14046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D34" t="s">
         <v>38</v>
       </c>
@@ -14104,7 +14107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D35" t="s">
         <v>39</v>
       </c>
@@ -14165,7 +14168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
       <c r="B36" t="s">
         <v>14</v>
       </c>
@@ -14232,7 +14235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D37" t="s">
         <v>24</v>
       </c>
@@ -14293,7 +14296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D38" t="s">
         <v>38</v>
       </c>
@@ -14354,7 +14357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D39" t="s">
         <v>39</v>
       </c>
@@ -14415,7 +14418,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
         <v>15</v>
       </c>
@@ -14482,7 +14485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D41" t="s">
         <v>24</v>
       </c>
@@ -14543,7 +14546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D42" t="s">
         <v>38</v>
       </c>
@@ -14604,7 +14607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D43" t="s">
         <v>39</v>
       </c>
@@ -14665,7 +14668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>16</v>
       </c>
@@ -14735,7 +14738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D45" t="s">
         <v>24</v>
       </c>
@@ -14796,7 +14799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D46" t="s">
         <v>38</v>
       </c>
@@ -14857,7 +14860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.4">
       <c r="D47" t="s">
         <v>39</v>
       </c>
@@ -14918,7 +14921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
         <v>18</v>
       </c>
@@ -14985,7 +14988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D49" t="s">
         <v>24</v>
       </c>
@@ -15046,7 +15049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D50" t="s">
         <v>38</v>
       </c>
@@ -15107,7 +15110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D51" t="s">
         <v>39</v>
       </c>
@@ -15168,7 +15171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
         <v>19</v>
       </c>
@@ -15235,7 +15238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D53" t="s">
         <v>24</v>
       </c>
@@ -15296,7 +15299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D54" t="s">
         <v>38</v>
       </c>
@@ -15357,7 +15360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.4">
       <c r="D55" t="s">
         <v>39</v>
       </c>
